--- a/十全特好_7-9月完整排程月曆.xlsx
+++ b/十全特好_7-9月完整排程月曆.xlsx
@@ -11,7 +11,8 @@
     <sheet name="📘 FB 貼文完整稿" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="💬 LINE OA 推播完整稿" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="🤖 LINE 自動序列" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="📌 圖例說明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="🛒 蝦皮MOMO活動完整稿" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="📌 圖例說明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="24">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +79,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDDCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA070"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FF9966"/>
       </patternFill>
     </fill>
@@ -98,7 +109,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF5522"/>
+        <fgColor rgb="00FF8050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF8060"/>
       </patternFill>
     </fill>
     <fill>
@@ -108,7 +124,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FABBA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9B0EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC88DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFD0B0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BB66CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,12 +169,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F79A80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7060"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C48DE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFBC94"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FF4411"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9080"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,6 +220,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B71C1C"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +283,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -229,20 +298,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -253,32 +319,86 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -647,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -819,32 +939,83 @@
       <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="100" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2025/7/1</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>活動開跑</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>十全好食節開跑｜任 2 件 9 折 + 蝦幣回饋</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>【活動期間】7/1–7/25
+【主打商品】即飲果醋 + 蒟蒻飲組合
+【優惠】任選 2 件 9 折 + 蝦幣回饋
+【配合動作】訂單包裝內夾官網入會 QR Code 卡</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>上架前確認商品頁圖片與活動標籤設定</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>訂單數、新客比例</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025/7/11</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>7/15 開抽，倒數 4 天</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>7/15 開抽，倒數 4 天。
 這次抽 300 名，名額比你想的多，
@@ -855,51 +1026,51 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>圖片：「倒數 4 天」大字設計，搭配獎品圖
 Olivia：朱紅底，「倒數 4 天」極大白字，下方一行小字說明資格｜緊迫感、數字要大</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="100" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>2025/7/11</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>7/15 開抽，倒數 4 天</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>7/15 開抽，還有 4 天。
 資格確認方法：登入官網，有帳號就 OK。
@@ -907,46 +1078,46 @@
 👇 確認資格</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>連結點擊數</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025/7/15</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>第一次抽獎得獎公告，300 名出爐</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>第一批 300 位，出爐了。
 感謝這個月加入的每一位新會員，
@@ -957,51 +1128,51 @@
 得獎名單查詢：[連結]</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>圖片：「恭喜 300 位得獎」簡潔圖卡，品牌色系
 Olivia：深醬色底，「恭喜 300 位」金色字，溫暖收穫感｜慶祝感、金色點綴</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2025/7/15</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>第一次抽獎 300 名得獎公告</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>第一批 300 位，出來了。
 得獎名單 → [連結]
@@ -1009,46 +1180,46 @@
 下次買直接用。8/15 還有一次。</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="100" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025/7/18</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>味噌湯不只一種喝法，三個懶人版本</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>味噌湯不只一種喝法。
 最懶版：味噌 + 豆腐 + 蔥花，三分鐘。
@@ -1060,51 +1231,51 @@
 比想像中好喝，你試試。</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>圖片：三種版本的味噌湯並排
 Olivia：三碗味噌湯並排俯拍，分別標「3 分鐘」「進階版」「冷湯」｜清晰對比、三等分構圖</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2025/7/22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>味醂不是米酒，差在哪裡</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>很多人把味醂當米酒用，錯了。
 米酒：去腥，讓肉軟一點。
@@ -1115,51 +1286,51 @@
 看看顏色和味道差在哪。</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>圖片：照燒肉特寫，油亮光澤感明顯
 Olivia：照燒豬肉特寫，油亮光澤，右側文字框說明味醂功效｜食材光澤、文字輔助</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025/7/25</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>8 月抽獎預告，資格自動保留到 9 月</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>7 月抽完了，8 月繼續。
 8/15 第二次抽獎，還是 300 名，
@@ -1171,51 +1342,51 @@
 還沒加入的，現在是第二次機會。</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>圖片：三個月抽獎時間軸圖卡
 Olivia：三格時間軸圖卡（7/15 ✓ 綠勾、8/15 圓圈、9/15 圓圈），朱紅強調下兩場｜進度感、視覺清楚</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>連結點擊數、分享數</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11" ht="100" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2025/7/25</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>活動預告</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>8 月抽獎 + 中元禮盒預熱</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>下週開始，我們有兩件事要跟你說：
 8/15 第二次抽獎，還有 300 名。
@@ -1223,46 +1394,96 @@
 都不用特別做什麼，繼續待著就好。</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>訊息開啟率</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2025/7/25</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>活動收尾</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>好食節收尾倒數｜8 月中元預告</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>【動作】更新商品頁 Banner 預告 8 月中元活動
+【文案方向】「好食節感謝，中元好料即將登場」
+【注意】確保庫存備貨到位</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>更新蝦皮店頭 Banner</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>下午 2:00</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>頁面瀏覽數</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2025/7/4</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>夏天一鍋涼拌，米醋是關鍵</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>不開火也能吃得很好。
 小黃瓜拍碎，加蒜末、辣椒、一匙米醋、少許鹽。
@@ -1272,51 +1493,51 @@
 這道夏天每週至少做兩次，你試試。</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>圖片：成品俯拍，自然光，不要太精緻感
 Olivia：小黃瓜涼拌俯拍，自然光，米白碗，木桌背景，左上角小字「5 分鐘料理」｜清爽感、夏天色調</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="100" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2025/7/8</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>你家的烏醋是釀的還是調的？</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>翻一下你家烏醋的成分表。
 第幾行出現「焦糖色素」？
@@ -1326,51 +1547,51 @@
 不是每瓶烏醋都一樣，只是大部分人沒有翻過成分表。</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>圖片：兩瓶烏醋成分表並排對比，文字清晰可讀
 Olivia：兩瓶醋並排，成分表各自清楚可讀，深青綠底條做區隔｜對比感強、文字清晰</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>2025/8/1</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>中元普渡三道家常菜，食材不浪費</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>中元普渡快到了，拜拜完的食材怎麼辦？
 三道不浪費的家常菜：
@@ -1383,51 +1604,152 @@
 拜完直接煮，不用另外買食材。</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>圖片：三道菜並排，家常感
 Olivia：三道菜三格構圖，每格一道，左上角各標菜名，家常實物感｜三等分、豐盛感</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr"/>
-    </row>
-    <row r="15" ht="100" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/10</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>活動預告</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購倒數預告｜8/12–8/14 每天 2 小時限時</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>【預告內容】8/12、8/13、8/14 每天 14:00–16:00 閃購
+【主打商品】味噌 + 烏醋 + 辣椒醬三件組
+【預告動作】限時動態 + 商品頁倒數標籤</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>設定蝦皮閃購時段，確認庫存</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>加購清單數</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr"/>
+    </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>2025/8/10</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>商品上架</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>中元禮盒上架｜滿 1,200 免運 + 贈品</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>【商品】中元天然調味禮盒（味噌 + 烏醋 + 辣椒醬）
+【定價】與官網同步
+【優惠】滿 1,200 免運 + 贈品（小包裝試用品）
+【圖片】使用官網禮盒實物圖</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>確認 MOMO 商品頁審核通過，圖片規格符合平台要求</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>商品頁瀏覽數、加購數</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>2025/8/12</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天。
 7 月已經抽了 300 名，
@@ -1439,51 +1761,51 @@
 👉 官網加入連結在留言區</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>圖片：「倒數 3 天」+ 累計已抽 300 名圖卡
 Olivia：朱紅底，「倒數 3 天」白字大，下方進度條「600/900」｜緊迫感、累積進度</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr"/>
-    </row>
-    <row r="16" ht="100" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr"/>
+    </row>
+    <row r="20" ht="100" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>2025/8/12</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>8/15 開抽，倒數 3 天</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天。
 7 月已抽了 300 名，這次再抽 300 名。
@@ -1491,46 +1813,199 @@
 👇 用 LINE 一鍵加入</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="G20" s="25" t="inlineStr"/>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>連結點擊數</t>
         </is>
       </c>
-      <c r="J16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17" ht="100" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="J20" s="24" t="inlineStr"/>
+    </row>
+    <row r="21" ht="100" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/12</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 1｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【商品】味噌 + 烏醋 + 辣椒醬三件組
+【配合】同步在 LINE OA 提醒好友</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>閃購期間監控庫存與訂單狀況</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、GMV</t>
+        </is>
+      </c>
+      <c r="J21" s="19" t="inlineStr"/>
+    </row>
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/13</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 2｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【商品】同 Day 1
+【加碼】留評價送小禮（若庫存允許）</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>確認 Day 1 庫存餘量，調整 Day 2 數量</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、評價數</t>
+        </is>
+      </c>
+      <c r="J22" s="19" t="inlineStr"/>
+    </row>
+    <row r="23" ht="100" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/14</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 3（最終場）｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【文案】「今天最後一場，明天恢復原價」
+【配合】FB + LINE OA 最後提醒</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>最後一天加強社群提醒力道</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、三天累計 GMV</t>
+        </is>
+      </c>
+      <c r="J23" s="19" t="inlineStr"/>
+    </row>
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>2025/8/15</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>第二次抽獎公告，累計 600 名得獎</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>第二批 300 位，出爐了。
 兩個月，累計 600 位得獎會員。
@@ -1541,51 +2016,51 @@
 得獎名單查詢：[連結]</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>圖片：「累計 600 位得獎」圖卡，有進度感
 Olivia：深醬色底，「累計 600 位得獎」金字，中間進度條已填 2/3｜進度感、溫暖</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="100" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25" ht="100" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>2025/8/15</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>第二次抽獎 300 名得獎公告，累計 600 名</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>第二批 300 位，出爐了。
 兩個月累計 600 位得獎。
@@ -1593,46 +2068,96 @@
 9/15 最後一次，300 名，資格自動保留。</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="G25" s="25" t="inlineStr"/>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I25" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19" ht="100" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="J25" s="24" t="inlineStr"/>
+    </row>
+    <row r="26" ht="100" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>2025/8/15</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>節慶衝單</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>中元禮盒主力日｜配合抽獎公告衝單</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>【動作】配合 FB + LINE 抽獎公告，在 MOMO 同步推廣
+【文案方向】「送禮送健康，天然調味全家用」
+【可申請】MOMO 節慶聯合檔期（若有補貼）</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>查詢 MOMO 8 月是否有聯合檔期補貼可申請</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>當日訂單數、禮盒銷售佔比</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr"/>
+    </row>
+    <row r="27" ht="100" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>2025/8/19</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>辣椒醬不只沾著吃，三種懶人料理</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>辣椒醬不只是沾醬。
 三種懶人用法：
@@ -1648,51 +2173,51 @@
 一瓶用三種方式，物超所值。</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>圖片：三種料理並排
 Olivia：三種料理橫排或三格，蛤蜊/拌麵/烤雞各一，自然光｜豐富感、料理質感</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H27" s="17" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="100" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="J27" s="17" t="inlineStr"/>
+    </row>
+    <row r="28" ht="100" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>2025/8/22</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>釀造醋 vs 調製醋，成分表不會說謊</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>買醋之前，先翻成分表。
 調製醋：水、醋酸、焦糖色素、調味劑。
@@ -1703,51 +2228,51 @@
 是叫你養成翻成分表的習慣。</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>圖片：兩種成分表並排對比
 Olivia：成分表兩欄並排，左側打 ✗，右側打 ✓，深青綠底強調｜對比清晰、判斷感</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21" ht="100" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr"/>
+    </row>
+    <row r="29" ht="100" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>2025/8/22</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>食譜推播</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>本月最多人存的食譜：辣椒醬三種懶人料理</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>這個月 FB 最多人存的一篇：
 「辣椒醬三種懶人料理」
@@ -1755,46 +2280,46 @@
 👇 看完整食譜</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="G29" s="25" t="inlineStr"/>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I29" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、回覆數</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
-    </row>
-    <row r="22" ht="100" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr"/>
+    </row>
+    <row r="30" ht="100" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>2025/8/26</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>9/15 最終場預告 + 中秋禮盒預熱</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>9/15 是最後一次，第三次抽獎。
 三個月抽了 600 名，
@@ -1806,51 +2331,51 @@
 詳情下週公布，先追蹤不要錯過。</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>圖片：一半中秋氛圍、一半抽獎倒數
 Olivia：上半中秋月亮氛圍，下半「最終場 9/15」倒數，分割構圖｜雙主題、視覺切割</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>追蹤數、分享數</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="100" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31" ht="100" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>2025/8/5</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>中元禮盒開賣，會員早鳥優惠</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>中元節送禮，送什麼不失禮？
 健康調味禮盒，對象是全家都能用的：
@@ -1862,51 +2387,51 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>圖片：禮盒實物正面，質感包裝
 Olivia：禮盒正面大圖，乾淨白底，右側文字「會員早鳥」紅色標籤｜產品主角、標籤搶眼</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="100" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32" ht="100" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>2025/8/5</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>禮盒限定</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E32" s="25" t="inlineStr">
         <is>
           <t>中元禮盒 LINE 好友早鳥（比 FB 早一天）</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>中元禮盒今天開賣，LINE 好友專屬早鳥價。
 FB 明天才公告，你早一天看到。
@@ -1914,46 +2439,46 @@
 👇 禮盒頁面</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="G32" s="25" t="inlineStr"/>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I32" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、訂單數</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr"/>
-    </row>
-    <row r="25" ht="100" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="J32" s="24" t="inlineStr"/>
+    </row>
+    <row r="33" ht="100" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>2025/8/8</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>辣椒醬成分表，你上次看是什麼時候</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>辣椒醬的成分表，你上次看是什麼時候？
 常見的：辣椒、大豆油、防腐劑、調味劑、色素。
@@ -1965,51 +2490,51 @@
 很少回頭買合成的。</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>圖片：成分表對比圖，文字要夠大夠清楚
 Olivia：辣椒醬瓶身 + 成分表放大，兩欄對比，左合成右天然｜對比版面、文字大</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26" ht="100" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr"/>
+    </row>
+    <row r="34" ht="100" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>2025/9/12</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>好的味噌，需要時間</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>好的味噌，需要時間。
 黃豆、米麴、鹽，
@@ -2022,51 +2547,152 @@
 你的舌頭會告訴你差在哪。</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G34" s="31" t="inlineStr">
         <is>
           <t>圖片：釀造過程質感照
 Olivia：木桶或陶甕，靜物感，柔和打光，日系工藝質感｜時間感、工藝感</t>
         </is>
       </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="H34" s="30" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="I34" s="31" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr"/>
-    </row>
-    <row r="27" ht="100" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="J34" s="30" t="inlineStr"/>
+    </row>
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>2025/9/12</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>正式開賣</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>中秋禮盒正式開賣（與官網同步）</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>【動作】早鳥結束，恢復原價開賣
+【配合】FB + LINE OA 同步公告
+【文案】「中秋送禮，天然調味料用一整年」
+【注意】確保物流在中秋前 3 天可到貨</t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="inlineStr">
+        <is>
+          <t>確認物流時效，中秋前 3 天截單</t>
+        </is>
+      </c>
+      <c r="H35" s="32" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I35" s="34" t="inlineStr">
+        <is>
+          <t>中秋期間總訂單數、GMV</t>
+        </is>
+      </c>
+      <c r="J35" s="32" t="inlineStr"/>
+    </row>
+    <row r="36" ht="100" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/12</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>節慶衝單</t>
+        </is>
+      </c>
+      <c r="E36" s="36" t="inlineStr">
+        <is>
+          <t>中秋正式開賣｜主力推廣日</t>
+        </is>
+      </c>
+      <c r="F36" s="36" t="inlineStr">
+        <is>
+          <t>【動作】與蝦皮、官網同步開賣
+【MOMO 特色】主打禮盒送禮情境，文案偏「送給爸媽」
+【可申請】MOMO 中秋聯合檔期（若有補貼）</t>
+        </is>
+      </c>
+      <c r="G36" s="36" t="inlineStr">
+        <is>
+          <t>查詢 MOMO 9 月中秋聯合檔期補貼，截止申請日期</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I36" s="36" t="inlineStr">
+        <is>
+          <t>當日訂單數、GMV</t>
+        </is>
+      </c>
+      <c r="J36" s="35" t="inlineStr"/>
+    </row>
+    <row r="37" ht="100" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>2025/9/15</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>最終場抽獎公告，累計 900 名得獎，感謝支持</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
         <is>
           <t>最後一批，300 位，出爐了。
 三個月，三次抽獎，
@@ -2079,51 +2705,51 @@
 下一個活動，等我們。</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="G37" s="31" t="inlineStr">
         <is>
           <t>圖片：「累計 900 位得獎，感謝支持」溫暖收尾圖卡
 Olivia：深醬色底，「累計 900 位，謝謝你們」金字，溫暖收尾｜感謝感、完結感</t>
         </is>
       </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="I37" s="31" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
-      <c r="J27" s="19" t="inlineStr"/>
-    </row>
-    <row r="28" ht="100" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="J37" s="30" t="inlineStr"/>
+    </row>
+    <row r="38" ht="100" customHeight="1">
+      <c r="A38" s="37" t="inlineStr">
         <is>
           <t>2025/9/15</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E38" s="38" t="inlineStr">
         <is>
           <t>最終場 300 名得獎公告，累計 900 名感謝</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F38" s="38" t="inlineStr">
         <is>
           <t>最後一批 300 位，出爐了。
 三個月，900 位得獎，謝謝你們。
@@ -2132,46 +2758,96 @@
 10 月見。</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr"/>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="G38" s="38" t="inlineStr"/>
+      <c r="H38" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I38" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29" ht="100" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="J38" s="37" t="inlineStr"/>
+    </row>
+    <row r="39" ht="100" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/17</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>活動收尾</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>中秋禮盒最後衝刺｜中秋前 2 天截單</t>
+        </is>
+      </c>
+      <c r="F39" s="36" t="inlineStr">
+        <is>
+          <t>【動作】更新商品頁「中秋前 2 天下單才來得及」緊迫文案
+【配合】FB + LINE 同步提醒
+【截單時間】9/17 23:59</t>
+        </is>
+      </c>
+      <c r="G39" s="36" t="inlineStr">
+        <is>
+          <t>確認物流可在 9/19 前到貨，超過截止下架禮盒</t>
+        </is>
+      </c>
+      <c r="H39" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>最終累計訂單數、中秋期間總 GMV</t>
+        </is>
+      </c>
+      <c r="J39" s="35" t="inlineStr"/>
+    </row>
+    <row r="40" ht="100" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>2025/9/19</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>秋天一鍋味噌豬肉湯，周末煮一次</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>天氣一涼，就想煮這鍋。
 味噌豬肉湯，周末煮一次，
@@ -2186,51 +2862,51 @@
 你會一直煮。</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G40" s="31" t="inlineStr">
         <is>
           <t>圖片：熱湯冒煙的溫暖感，秋天色調
 Olivia：味噌豬肉湯，蒸氣冒煙，秋天橘調光線，木碗或陶碗｜暖色、食慾感</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="H40" s="30" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="I40" s="31" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr"/>
-    </row>
-    <row r="30" ht="100" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="J40" s="30" t="inlineStr"/>
+    </row>
+    <row r="41" ht="100" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>2025/9/2</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒正式開賣，會員優先購</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F41" s="31" t="inlineStr">
         <is>
           <t>中秋送禮，今年換個思路。
 月餅吃完就忘，
@@ -2243,51 +2919,51 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G41" s="31" t="inlineStr">
         <is>
           <t>圖片：禮盒與中秋氛圍結合
 Olivia：禮盒 + 月亮背景，深夜質感，右側「會員優先購」標籤｜中秋氛圍、禮品感</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="H41" s="30" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr">
+      <c r="I41" s="31" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr"/>
-    </row>
-    <row r="31" ht="100" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr"/>
+    </row>
+    <row r="42" ht="100" customHeight="1">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>2025/9/2</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C42" s="37" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D42" s="29" t="inlineStr">
         <is>
           <t>禮盒限定</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E42" s="38" t="inlineStr">
         <is>
           <t>中秋禮盒 LINE 好友早鳥（比 FB 早一天）</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F42" s="38" t="inlineStr">
         <is>
           <t>中秋禮盒今天開賣。
 LINE 好友專屬早鳥連結在下面，比 FB 早一天。
@@ -2295,46 +2971,46 @@
 👇</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr"/>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="G42" s="38" t="inlineStr"/>
+      <c r="H42" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I42" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、訂單數</t>
         </is>
       </c>
-      <c r="J31" s="21" t="inlineStr"/>
-    </row>
-    <row r="32" ht="100" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="J42" s="37" t="inlineStr"/>
+    </row>
+    <row r="43" ht="100" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>2025/9/23</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒最後機會 + 雙十會員搶先看預告</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F43" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒，最後幾天。
 還沒送的，今天訂，還來得及。
@@ -2346,51 +3022,51 @@
 👉 中秋禮盒連結在留言區</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G43" s="31" t="inlineStr">
         <is>
           <t>圖片：中秋收尾 + 雙十倒數感
 Olivia：左禮盒、右「雙十預告」箭頭指向，分割畫面設計｜兩個訊息並陳</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr">
+      <c r="H43" s="30" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I43" s="31" t="inlineStr">
         <is>
           <t>連結點擊數、追蹤數</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr"/>
-    </row>
-    <row r="33" ht="100" customHeight="1">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="J43" s="30" t="inlineStr"/>
+    </row>
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>2025/9/23</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C44" s="37" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>活動預告</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E44" s="38" t="inlineStr">
         <is>
           <t>雙十會員搶先看預告</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F44" s="38" t="inlineStr">
         <is>
           <t>雙十連假，十全有東西要給你。
 細節下週公布，官網會員才看得到。
@@ -2398,46 +3074,46 @@
 👇</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr"/>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="G44" s="38" t="inlineStr"/>
+      <c r="H44" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I44" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、加入會員數</t>
         </is>
       </c>
-      <c r="J33" s="21" t="inlineStr"/>
-    </row>
-    <row r="34" ht="100" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="J44" s="37" t="inlineStr"/>
+    </row>
+    <row r="45" ht="100" customHeight="1">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>2025/9/26</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？看這三個字就夠了</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F45" s="31" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？
 看這三個字就夠了。
@@ -2451,51 +3127,51 @@
 「釀造」兩個字在不在，答案就出來了。</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G45" s="31" t="inlineStr">
         <is>
           <t>圖片：成分表特寫，「釀造」兩個字清楚圈出
 Olivia：成分表特寫，紅圈圈出「釀造」兩字，深青綠底色｜聚焦細節、強調字</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H45" s="30" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="I45" s="31" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J34" s="19" t="inlineStr"/>
-    </row>
-    <row r="35" ht="100" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="J45" s="30" t="inlineStr"/>
+    </row>
+    <row r="46" ht="100" customHeight="1">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>2025/9/30</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C46" s="37" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D46" s="39" t="inlineStr">
         <is>
           <t>暖場</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E46" s="38" t="inlineStr">
         <is>
           <t>10 月有好東西，先追蹤不要錯過</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t>十月，我們有好東西要給你。
 細節下週公布，官網會員才看得到。
@@ -2503,46 +3179,46 @@
 👇 用 LINE 一鍵加入會員</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr"/>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="G46" s="38" t="inlineStr"/>
+      <c r="H46" s="37" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="I46" s="38" t="inlineStr">
         <is>
           <t>訊息開啟率</t>
         </is>
       </c>
-      <c r="J35" s="21" t="inlineStr"/>
-    </row>
-    <row r="36" ht="100" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="J46" s="37" t="inlineStr"/>
+    </row>
+    <row r="47" ht="100" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>2025/9/5</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>中秋烤肉醬自己調，烏醋 + 辣椒醬</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F47" s="31" t="inlineStr">
         <is>
           <t>中秋烤肉，醬料自己調的和買的，差一個層次。
 基底烤肉醬配方：
@@ -2554,51 +3230,153 @@
 比瓶裝烤肉醬好吃，成本少很多。</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="G47" s="31" t="inlineStr">
         <is>
           <t>圖片：烤肉實境，搭配醬料小碗
 Olivia：烤肉現場俯拍，炭火煙霧感，小碗自調醬料放前景｜煙霧感、生活感強</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="H47" s="30" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="I36" s="20" t="inlineStr">
+      <c r="I47" s="31" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr"/>
-    </row>
-    <row r="37" ht="100" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="J47" s="30" t="inlineStr"/>
+    </row>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>2025/9/8</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>早鳥預購</t>
+        </is>
+      </c>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>中秋早鳥預購開始｜9/8–9/10 限定 9 折</t>
+        </is>
+      </c>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>【活動期間】9/8–9/10
+【折扣】早鳥 9 折
+【主打商品】味噌 + 味醂 + 烏醋 + 米醋四件組
+【加碼】前 100 組附「烤肉醬食譜卡」
+【定價原則】不低於官網會員價</t>
+        </is>
+      </c>
+      <c r="G48" s="34" t="inlineStr">
+        <is>
+          <t>設定早鳥折扣碼，確認食譜卡印製數量</t>
+        </is>
+      </c>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I48" s="34" t="inlineStr">
+        <is>
+          <t>預購訂單數</t>
+        </is>
+      </c>
+      <c r="J48" s="32" t="inlineStr"/>
+    </row>
+    <row r="49" ht="100" customHeight="1">
+      <c r="A49" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/8</t>
+        </is>
+      </c>
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>商品上架</t>
+        </is>
+      </c>
+      <c r="E49" s="36" t="inlineStr">
+        <is>
+          <t>中秋禮盒上架｜滿 2,000 加購優惠</t>
+        </is>
+      </c>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>【商品】中秋天然調味禮盒（味噌 + 味醂 + 烏醋 + 米醋四件組）
+【優惠】滿 2,000 加購第二件 75 折
+【目標客群】30–55 歲，送禮給長輩或朋友</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>確認 MOMO 商品頁上架，主圖需有中秋氛圍</t>
+        </is>
+      </c>
+      <c r="H49" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>商品頁瀏覽數、加購數</t>
+        </is>
+      </c>
+      <c r="J49" s="35" t="inlineStr"/>
+    </row>
+    <row r="50" ht="100" customHeight="1">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>2025/9/9</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
         <is>
           <t>最終場抽獎倒數 6 天，這次沒加入就真的沒了</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F50" s="31" t="inlineStr">
         <is>
           <t>9/15，最後一次。
 三個月，共三次抽獎，每次 300 名。
@@ -2612,51 +3390,51 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="G37" s="20" t="inlineStr">
+      <c r="G50" s="31" t="inlineStr">
         <is>
           <t>圖片：「最終場 倒數 6 天」大字圖卡
 Olivia：朱紅底，「最終場 倒數 6 天」白字極大，緊張感拉滿｜最大衝擊感</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="H50" s="30" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I37" s="20" t="inlineStr">
+      <c r="I50" s="31" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr"/>
-    </row>
-    <row r="38" ht="100" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="J50" s="30" t="inlineStr"/>
+    </row>
+    <row r="51" ht="100" customHeight="1">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>2025/9/9</t>
         </is>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B51" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C51" s="37" t="inlineStr">
         <is>
           <t>LINE OA</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E51" s="38" t="inlineStr">
         <is>
           <t>最終場 9/15，倒數 6 天</t>
         </is>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F51" s="38" t="inlineStr">
         <is>
           <t>9/15 最後一次抽獎，倒數 6 天。
 三個月共抽 900 名，最後這批 300 名。
@@ -2665,18 +3443,18 @@
 👇</t>
         </is>
       </c>
-      <c r="G38" s="22" t="inlineStr"/>
-      <c r="H38" s="21" t="inlineStr">
+      <c r="G51" s="38" t="inlineStr"/>
+      <c r="H51" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I51" s="38" t="inlineStr">
         <is>
           <t>連結點擊數</t>
         </is>
       </c>
-      <c r="J38" s="21" t="inlineStr"/>
+      <c r="J51" s="37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2708,67 +3486,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>編號</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="41" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="41" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="41" t="inlineStr">
         <is>
           <t>主題</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="41" t="inlineStr">
         <is>
           <t>主打商品</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="G1" s="41" t="inlineStr">
         <is>
           <t>貼文內文</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="H1" s="41" t="inlineStr">
         <is>
           <t>Hashtag</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="I1" s="41" t="inlineStr">
         <is>
           <t>圖片建議</t>
         </is>
       </c>
-      <c r="J1" s="25" t="inlineStr">
+      <c r="J1" s="42" t="inlineStr">
         <is>
           <t>配圖方向（Olivia）</t>
         </is>
       </c>
-      <c r="K1" s="25" t="inlineStr">
+      <c r="K1" s="42" t="inlineStr">
         <is>
           <t>重點元素</t>
         </is>
       </c>
-      <c r="L1" s="25" t="inlineStr">
+      <c r="L1" s="42" t="inlineStr">
         <is>
           <t>發文時間</t>
         </is>
       </c>
-      <c r="M1" s="25" t="inlineStr">
+      <c r="M1" s="42" t="inlineStr">
         <is>
           <t>追蹤指標</t>
         </is>
@@ -2824,22 +3602,22 @@
           <t>獎品實物 + 倒數「14 天」字樣</t>
         </is>
       </c>
-      <c r="J2" s="26" t="inlineStr">
+      <c r="J2" s="43" t="inlineStr">
         <is>
           <t>朱紅底，白字「倒數 14 天」佔畫面 50%，獎品實物放右側</t>
         </is>
       </c>
-      <c r="K2" s="26" t="inlineStr">
+      <c r="K2" s="43" t="inlineStr">
         <is>
           <t>大數字、獎品照</t>
         </is>
       </c>
-      <c r="L2" s="26" t="inlineStr">
+      <c r="L2" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M2" s="26" t="inlineStr">
+      <c r="M2" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
@@ -2859,7 +3637,7 @@
           <t>五</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
@@ -2894,22 +3672,22 @@
           <t>成品俯拍，自然光，不要太精緻感</t>
         </is>
       </c>
-      <c r="J3" s="26" t="inlineStr">
+      <c r="J3" s="43" t="inlineStr">
         <is>
           <t>小黃瓜涼拌俯拍，自然光，米白碗，木桌背景，左上角小字「5 分鐘料理」</t>
         </is>
       </c>
-      <c r="K3" s="26" t="inlineStr">
+      <c r="K3" s="43" t="inlineStr">
         <is>
           <t>清爽感、夏天色調</t>
         </is>
       </c>
-      <c r="L3" s="26" t="inlineStr">
+      <c r="L3" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M3" s="26" t="inlineStr">
+      <c r="M3" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
@@ -2929,7 +3707,7 @@
           <t>二</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
@@ -2964,22 +3742,22 @@
           <t>兩瓶烏醋成分表並排對比，文字清晰可讀</t>
         </is>
       </c>
-      <c r="J4" s="26" t="inlineStr">
+      <c r="J4" s="43" t="inlineStr">
         <is>
           <t>兩瓶醋並排，成分表各自清楚可讀，深青綠底條做區隔</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="43" t="inlineStr">
         <is>
           <t>對比感強、文字清晰</t>
         </is>
       </c>
-      <c r="L4" s="26" t="inlineStr">
+      <c r="L4" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
@@ -3035,22 +3813,22 @@
           <t>「倒數 4 天」大字設計，搭配獎品圖</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>朱紅底，「倒數 4 天」極大白字，下方一行小字說明資格</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr">
         <is>
           <t>緊迫感、數字要大</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="L5" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
@@ -3106,22 +3884,22 @@
           <t>「恭喜 300 位得獎」簡潔圖卡，品牌色系</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="J6" s="43" t="inlineStr">
         <is>
           <t>深醬色底，「恭喜 300 位」金色字，溫暖收穫感</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="43" t="inlineStr">
         <is>
           <t>慶祝感、金色點綴</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="L6" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="M6" s="43" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
@@ -3141,7 +3919,7 @@
           <t>五</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
@@ -3178,22 +3956,22 @@
           <t>三種版本的味噌湯並排</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="J7" s="43" t="inlineStr">
         <is>
           <t>三碗味噌湯並排俯拍，分別標「3 分鐘」「進階版」「冷湯」</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="43" t="inlineStr">
         <is>
           <t>清晰對比、三等分構圖</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="L7" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="43" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
@@ -3213,7 +3991,7 @@
           <t>二</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
@@ -3249,22 +4027,22 @@
           <t>照燒肉特寫，油亮光澤感明顯</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="J8" s="43" t="inlineStr">
         <is>
           <t>照燒豬肉特寫，油亮光澤，右側文字框說明味醂功效</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="43" t="inlineStr">
         <is>
           <t>食材光澤、文字輔助</t>
         </is>
       </c>
-      <c r="L8" s="26" t="inlineStr">
+      <c r="L8" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="43" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
@@ -3321,57 +4099,57 @@
           <t>三個月抽獎時間軸圖卡</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="43" t="inlineStr">
         <is>
           <t>三格時間軸圖卡（7/15 ✓ 綠勾、8/15 圓圈、9/15 圓圈），朱紅強調下兩場</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="43" t="inlineStr">
         <is>
           <t>進度感、視覺清楚</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr">
+      <c r="M9" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、分享數</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>2025/8/1</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>中元普渡三道家常菜，食材不浪費</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>味噌、烏醋、辣椒醬</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>中元普渡快到了，拜拜完的食材怎麼辦？
 三道不浪費的家常菜：
@@ -3384,47 +4162,47 @@
 拜完直接煮，不用另外買食材。</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>#中元節 #普渡料理 #十全調味</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>三道菜並排，家常感</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="43" t="inlineStr">
         <is>
           <t>三道菜三格構圖，每格一道，左上角各標菜名，家常實物感</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="43" t="inlineStr">
         <is>
           <t>三等分、豐盛感</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr">
+      <c r="M10" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2025/8/5</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -3434,17 +4212,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>中元禮盒開賣，會員早鳥優惠</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>禮盒</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>中元節送禮，送什麼不失禮？
 健康調味禮盒，對象是全家都能用的：
@@ -3456,67 +4234,67 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>#中元送禮 #十全特好 #健康禮盒</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>禮盒實物正面，質感包裝</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="43" t="inlineStr">
         <is>
           <t>禮盒正面大圖，乾淨白底，右側文字「會員早鳥」紅色標籤</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="43" t="inlineStr">
         <is>
           <t>產品主角、標籤搶眼</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="13" t="n">
+      <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2025/8/8</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>辣椒醬成分表，你上次看是什麼時候</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>辣椒醬</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>辣椒醬的成分表，你上次看是什麼時候？
 常見的：辣椒、大豆油、防腐劑、調味劑、色素。
@@ -3528,47 +4306,47 @@
 很少回頭買合成的。</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>#成分控 #辣椒醬 #十全辣椒醬</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>成分表對比圖，文字要夠大夠清楚</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="J12" s="43" t="inlineStr">
         <is>
           <t>辣椒醬瓶身 + 成分表放大，兩欄對比，左合成右天然</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K12" s="43" t="inlineStr">
         <is>
           <t>對比版面、文字大</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="L12" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M12" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2025/8/12</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -3578,17 +4356,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天。
 7 月已經抽了 300 名，
@@ -3600,47 +4378,47 @@
 👉 官網加入連結在留言區</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎倒數 #會員限定</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>「倒數 3 天」+ 累計已抽 300 名圖卡</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="43" t="inlineStr">
         <is>
           <t>朱紅底，「倒數 3 天」白字大，下方進度條「600/900」</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="43" t="inlineStr">
         <is>
           <t>緊迫感、累積進度</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
     </row>
     <row r="14" ht="110" customHeight="1">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2025/8/15</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
@@ -3650,17 +4428,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>第二次抽獎公告，累計 600 名得獎</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>第二批 300 位，出爐了。
 兩個月，累計 600 位得獎會員。
@@ -3671,67 +4449,67 @@
 得獎名單查詢：[連結]</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎結果 #恭喜得獎</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>「累計 600 位得獎」圖卡，有進度感</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J14" s="43" t="inlineStr">
         <is>
           <t>深醬色底，「累計 600 位得獎」金字，中間進度條已填 2/3</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="43" t="inlineStr">
         <is>
           <t>進度感、溫暖</t>
         </is>
       </c>
-      <c r="L14" s="26" t="inlineStr">
+      <c r="L14" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr">
+      <c r="M14" s="43" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
     </row>
     <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2025/8/19</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>辣椒醬不只沾著吃，三種懶人料理</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>辣椒醬</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>辣椒醬不只是沾醬。
 三種懶人用法：
@@ -3747,67 +4525,67 @@
 一瓶用三種方式，物超所值。</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>#辣椒醬料理 #懶人食譜 #十全辣椒醬</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>三種料理並排</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="43" t="inlineStr">
         <is>
           <t>三種料理橫排或三格，蛤蜊/拌麵/烤雞各一，自然光</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="43" t="inlineStr">
         <is>
           <t>豐富感、料理質感</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr">
+      <c r="M15" s="43" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
     </row>
     <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025/8/22</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>釀造醋 vs 調製醋，成分表不會說謊</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>烏醋、米醋</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>買醋之前，先翻成分表。
 調製醋：水、醋酸、焦糖色素、調味劑。
@@ -3818,47 +4596,47 @@
 是叫你養成翻成分表的習慣。</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>#成分控 #釀造醋 #十全烏醋</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>兩種成分表並排對比</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J16" s="43" t="inlineStr">
         <is>
           <t>成分表兩欄並排，左側打 ✗，右側打 ✓，深青綠底強調</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K16" s="43" t="inlineStr">
         <is>
           <t>對比清晰、判斷感</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="L16" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr">
+      <c r="M16" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
     </row>
     <row r="17" ht="110" customHeight="1">
-      <c r="A17" s="13" t="n">
+      <c r="A17" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2025/8/26</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -3868,17 +4646,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>9/15 最終場預告 + 中秋禮盒預熱</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>全系列、禮盒</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>9/15 是最後一次，第三次抽獎。
 三個月抽了 600 名，
@@ -3890,47 +4668,47 @@
 詳情下週公布，先追蹤不要錯過。</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="18" t="inlineStr">
         <is>
           <t>#十全特好 #中秋禮盒 #抽獎最終場</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>一半中秋氛圍、一半抽獎倒數</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="43" t="inlineStr">
         <is>
           <t>上半中秋月亮氛圍，下半「最終場 9/15」倒數，分割構圖</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="43" t="inlineStr">
         <is>
           <t>雙主題、視覺切割</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="M17" s="43" t="inlineStr">
         <is>
           <t>追蹤數、分享數</t>
         </is>
       </c>
     </row>
     <row r="18" ht="110" customHeight="1">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>2025/9/2</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -3940,17 +4718,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒正式開賣，會員優先購</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>禮盒</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="31" t="inlineStr">
         <is>
           <t>中秋送禮，今年換個思路。
 月餅吃完就忘，
@@ -3963,67 +4741,67 @@
 👉 禮盒詳情在留言區</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>#中秋送禮 #十全特好 #天然調味禮盒</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>禮盒與中秋氛圍結合</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="J18" s="43" t="inlineStr">
         <is>
           <t>禮盒 + 月亮背景，深夜質感，右側「會員優先購」標籤</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="K18" s="43" t="inlineStr">
         <is>
           <t>中秋氛圍、禮品感</t>
         </is>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="L18" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M18" s="26" t="inlineStr">
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、私訊數</t>
         </is>
       </c>
     </row>
     <row r="19" ht="110" customHeight="1">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>2025/9/5</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>中秋烤肉醬自己調，烏醋 + 辣椒醬</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>烏醋、辣椒醬</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="31" t="inlineStr">
         <is>
           <t>中秋烤肉，醬料自己調的和買的，差一個層次。
 基底烤肉醬配方：
@@ -4035,47 +4813,47 @@
 比瓶裝烤肉醬好吃，成本少很多。</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="31" t="inlineStr">
         <is>
           <t>#中秋烤肉 #烤肉醬 #十全調味</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="I19" s="31" t="inlineStr">
         <is>
           <t>烤肉實境，搭配醬料小碗</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="43" t="inlineStr">
         <is>
           <t>烤肉現場俯拍，炭火煙霧感，小碗自調醬料放前景</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="43" t="inlineStr">
         <is>
           <t>煙霧感、生活感強</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr">
+      <c r="M19" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
       </c>
     </row>
     <row r="20" ht="110" customHeight="1">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>2025/9/9</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -4085,17 +4863,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>最終場抽獎倒數 6 天，這次沒加入就真的沒了</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="31" t="inlineStr">
         <is>
           <t>9/15，最後一次。
 三個月，共三次抽獎，每次 300 名。
@@ -4109,67 +4887,67 @@
 👉 加入連結在留言區</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="31" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎最終場 #倒數</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="31" t="inlineStr">
         <is>
           <t>「最終場 倒數 6 天」大字圖卡</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="J20" s="43" t="inlineStr">
         <is>
           <t>朱紅底，「最終場 倒數 6 天」白字極大，緊張感拉滿</t>
         </is>
       </c>
-      <c r="K20" s="26" t="inlineStr">
+      <c r="K20" s="43" t="inlineStr">
         <is>
           <t>最大衝擊感</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="L20" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M20" s="26" t="inlineStr">
+      <c r="M20" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
     </row>
     <row r="21" ht="110" customHeight="1">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>2025/9/12</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>好的味噌，需要時間</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="31" t="inlineStr">
         <is>
           <t>味噌</t>
         </is>
       </c>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>好的味噌，需要時間。
 黃豆、米麴、鹽，
@@ -4182,47 +4960,47 @@
 你的舌頭會告訴你差在哪。</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>#味噌 #發酵食品 #十全味噌</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="I21" s="31" t="inlineStr">
         <is>
           <t>釀造過程質感照</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="J21" s="43" t="inlineStr">
         <is>
           <t>木桶或陶甕，靜物感，柔和打光，日系工藝質感</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="K21" s="43" t="inlineStr">
         <is>
           <t>時間感、工藝感</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr">
+      <c r="M21" s="43" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
     </row>
     <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>2025/9/15</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>一</t>
         </is>
@@ -4232,17 +5010,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>最終場抽獎公告，累計 900 名得獎，感謝支持</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="31" t="inlineStr">
         <is>
           <t>最後一批，300 位，出爐了。
 三個月，三次抽獎，
@@ -4255,67 +5033,67 @@
 下一個活動，等我們。</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="31" t="inlineStr">
         <is>
           <t>#十全特好 #抽獎結果 #感謝支持</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="I22" s="31" t="inlineStr">
         <is>
           <t>「累計 900 位得獎，感謝支持」溫暖收尾圖卡</t>
         </is>
       </c>
-      <c r="J22" s="26" t="inlineStr">
+      <c r="J22" s="43" t="inlineStr">
         <is>
           <t>深醬色底，「累計 900 位，謝謝你們」金字，溫暖收尾</t>
         </is>
       </c>
-      <c r="K22" s="26" t="inlineStr">
+      <c r="K22" s="43" t="inlineStr">
         <is>
           <t>感謝感、完結感</t>
         </is>
       </c>
-      <c r="L22" s="26" t="inlineStr">
+      <c r="L22" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M22" s="26" t="inlineStr">
+      <c r="M22" s="43" t="inlineStr">
         <is>
           <t>留言數、分享數</t>
         </is>
       </c>
     </row>
     <row r="23" ht="110" customHeight="1">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>2025/9/19</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>食譜</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>秋天一鍋味噌豬肉湯，周末煮一次</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="31" t="inlineStr">
         <is>
           <t>味噌</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="31" t="inlineStr">
         <is>
           <t>天氣一涼，就想煮這鍋。
 味噌豬肉湯，周末煮一次，
@@ -4330,47 +5108,47 @@
 你會一直煮。</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>#秋天食譜 #味噌豬肉湯 #十全味噌</t>
         </is>
       </c>
-      <c r="I23" s="20" t="inlineStr">
+      <c r="I23" s="31" t="inlineStr">
         <is>
           <t>熱湯冒煙的溫暖感，秋天色調</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr">
+      <c r="J23" s="43" t="inlineStr">
         <is>
           <t>味噌豬肉湯，蒸氣冒煙，秋天橘調光線，木碗或陶碗</t>
         </is>
       </c>
-      <c r="K23" s="26" t="inlineStr">
+      <c r="K23" s="43" t="inlineStr">
         <is>
           <t>暖色、食慾感</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="L23" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr">
+      <c r="M23" s="43" t="inlineStr">
         <is>
           <t>儲存數、留言數</t>
         </is>
       </c>
     </row>
     <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>2025/9/23</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>二</t>
         </is>
@@ -4380,17 +5158,17 @@
           <t>活動</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒最後機會 + 雙十會員搶先看預告</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>禮盒、全系列</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="31" t="inlineStr">
         <is>
           <t>中秋禮盒，最後幾天。
 還沒送的，今天訂，還來得及。
@@ -4402,67 +5180,67 @@
 👉 中秋禮盒連結在留言區</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="31" t="inlineStr">
         <is>
           <t>#中秋禮盒 #十全特好 #雙十預告</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="31" t="inlineStr">
         <is>
           <t>中秋收尾 + 雙十倒數感</t>
         </is>
       </c>
-      <c r="J24" s="26" t="inlineStr">
+      <c r="J24" s="43" t="inlineStr">
         <is>
           <t>左禮盒、右「雙十預告」箭頭指向，分割畫面設計</t>
         </is>
       </c>
-      <c r="K24" s="26" t="inlineStr">
+      <c r="K24" s="43" t="inlineStr">
         <is>
           <t>兩個訊息並陳</t>
         </is>
       </c>
-      <c r="L24" s="26" t="inlineStr">
+      <c r="L24" s="43" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr">
+      <c r="M24" s="43" t="inlineStr">
         <is>
           <t>連結點擊數、追蹤數</t>
         </is>
       </c>
     </row>
     <row r="25" ht="110" customHeight="1">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>2025/9/26</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>知識</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？看這三個字就夠了</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>全系列</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="31" t="inlineStr">
         <is>
           <t>天然調味料怎麼挑？
 看這三個字就夠了。
@@ -4476,32 +5254,32 @@
 「釀造」兩個字在不在，答案就出來了。</t>
         </is>
       </c>
-      <c r="H25" s="20" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>#天然調味 #釀造 #十全特好</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="I25" s="31" t="inlineStr">
         <is>
           <t>成分表特寫，「釀造」兩個字清楚圈出</t>
         </is>
       </c>
-      <c r="J25" s="26" t="inlineStr">
+      <c r="J25" s="43" t="inlineStr">
         <is>
           <t>成分表特寫，紅圈圈出「釀造」兩字，深青綠底色</t>
         </is>
       </c>
-      <c r="K25" s="26" t="inlineStr">
+      <c r="K25" s="43" t="inlineStr">
         <is>
           <t>聚焦細節、強調字</t>
         </is>
       </c>
-      <c r="L25" s="26" t="inlineStr">
+      <c r="L25" s="43" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="M25" s="26" t="inlineStr">
+      <c r="M25" s="43" t="inlineStr">
         <is>
           <t>儲存數、分享數</t>
         </is>
@@ -4532,42 +5310,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>編號</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="44" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" s="44" t="inlineStr">
         <is>
           <t>星期</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D1" s="44" t="inlineStr">
         <is>
           <t>類型</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E1" s="44" t="inlineStr">
         <is>
           <t>主題</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="F1" s="44" t="inlineStr">
         <is>
           <t>完整訊息內容</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G1" s="44" t="inlineStr">
         <is>
           <t>發送時間</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H1" s="44" t="inlineStr">
         <is>
           <t>追蹤指標</t>
         </is>
@@ -4632,7 +5410,7 @@
           <t>五</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
@@ -4675,7 +5453,7 @@
           <t>二</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
@@ -4718,7 +5496,7 @@
           <t>五</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>活動預告</t>
         </is>
@@ -4748,30 +5526,30 @@
       </c>
     </row>
     <row r="6" ht="100" customHeight="1">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>2025/8/5</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>禮盒限定</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>中元禮盒 LINE 好友早鳥（比 FB 早一天）</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>中元禮盒今天開賣，LINE 好友專屬早鳥價。
 FB 明天才公告，你早一天看到。
@@ -4779,42 +5557,42 @@
 👇 禮盒頁面</t>
         </is>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、訂單數</t>
         </is>
       </c>
     </row>
     <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>2025/8/12</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>8/15 開抽，倒數 3 天</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>8/15 第二次抽獎，倒數 3 天。
 7 月已抽了 300 名，這次再抽 300 名。
@@ -4822,42 +5600,42 @@
 👇 用 LINE 一鍵加入</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="25" t="inlineStr">
         <is>
           <t>連結點擊數</t>
         </is>
       </c>
     </row>
     <row r="8" ht="100" customHeight="1">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>2025/8/15</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>第二次抽獎 300 名得獎公告，累計 600 名</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>第二批 300 位，出爐了。
 兩個月累計 600 位得獎。
@@ -4865,42 +5643,42 @@
 9/15 最後一次，300 名，資格自動保留。</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
     </row>
     <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>2025/8/22</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>五</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>食譜推播</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>本月最多人存的食譜：辣椒醬三種懶人料理</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>這個月 FB 最多人存的一篇：
 「辣椒醬三種懶人料理」
@@ -4908,42 +5686,42 @@
 👇 看完整食譜</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>連結點擊數、回覆數</t>
         </is>
       </c>
     </row>
     <row r="10" ht="100" customHeight="1">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>2025/9/2</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>禮盒限定</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>中秋禮盒 LINE 好友早鳥（比 FB 早一天）</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>中秋禮盒今天開賣。
 LINE 好友專屬早鳥連結在下面，比 FB 早一天。
@@ -4951,42 +5729,42 @@
 👇</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、訂單數</t>
         </is>
       </c>
     </row>
     <row r="11" ht="100" customHeight="1">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>2025/9/9</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>活動倒數</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>最終場 9/15，倒數 6 天</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="38" t="inlineStr">
         <is>
           <t>9/15 最後一次抽獎，倒數 6 天。
 三個月共抽 900 名，最後這批 300 名。
@@ -4995,42 +5773,42 @@
 👇</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="38" t="inlineStr">
         <is>
           <t>連結點擊數</t>
         </is>
       </c>
     </row>
     <row r="12" ht="100" customHeight="1">
-      <c r="A12" s="21" t="n">
+      <c r="A12" s="37" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>2025/9/15</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>一</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>得獎公告</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="38" t="inlineStr">
         <is>
           <t>最終場 300 名得獎公告，累計 900 名感謝</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>最後一批 300 位，出爐了。
 三個月，900 位得獎，謝謝你們。
@@ -5039,42 +5817,42 @@
 10 月見。</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、留言數</t>
         </is>
       </c>
     </row>
     <row r="13" ht="100" customHeight="1">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>2025/9/23</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>活動預告</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>雙十會員搶先看預告</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>雙十連假，十全有東西要給你。
 細節下週公布，官網會員才看得到。
@@ -5082,42 +5860,42 @@
 👇</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>早上 10:00</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="38" t="inlineStr">
         <is>
           <t>連結點擊數、加入會員數</t>
         </is>
       </c>
     </row>
     <row r="14" ht="100" customHeight="1">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>2025/9/30</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>二</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>暖場</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="38" t="inlineStr">
         <is>
           <t>10 月有好東西，先追蹤不要錯過</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>十月，我們有好東西要給你。
 細節下週公布，官網會員才看得到。
@@ -5125,12 +5903,12 @@
 👇 用 LINE 一鍵加入會員</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>晚上 7:30</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="38" t="inlineStr">
         <is>
           <t>訊息開啟率</t>
         </is>
@@ -5157,44 +5935,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>觸發時機</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>時間點</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>主題</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>完整訊息內容</t>
         </is>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>自動觸發</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="46" t="inlineStr">
         <is>
           <t>加入當下</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C2" s="47" t="inlineStr">
         <is>
           <t>新好友加入：立即歡迎 + 一鍵入會</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="47" t="inlineStr">
         <is>
           <t>嗨，歡迎加入！
 你已經在 LINE 了，官網會員一鍵就好。
@@ -5205,22 +5983,22 @@
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>自動觸發</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="46" t="inlineStr">
         <is>
           <t>加入後第 2 天</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="47" t="inlineStr">
         <is>
           <t>新好友未轉換：低摩擦再提醒</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="47" t="inlineStr">
         <is>
           <t>折扣券還沒領到？
 不用填表單，不用記密碼。
@@ -5230,22 +6008,22 @@
       </c>
     </row>
     <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>自動觸發</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>加入後第 5 天</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>新好友未轉換：最後提醒 + 抽獎緊迫感</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>最後提醒一次。
 7/15 抽獎只有官網會員才能參加，
@@ -5266,15 +6044,777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>編號</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>星期</t>
+        </is>
+      </c>
+      <c r="D1" s="48" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="E1" s="48" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="F1" s="48" t="inlineStr">
+        <is>
+          <t>活動主題</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
+        <is>
+          <t>活動內容</t>
+        </is>
+      </c>
+      <c r="H1" s="48" t="inlineStr">
+        <is>
+          <t>執行備注</t>
+        </is>
+      </c>
+      <c r="I1" s="48" t="inlineStr">
+        <is>
+          <t>發布時間</t>
+        </is>
+      </c>
+      <c r="J1" s="48" t="inlineStr">
+        <is>
+          <t>追蹤指標</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2025/7/1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>活動開跑</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>十全好食節開跑｜任 2 件 9 折 + 蝦幣回饋</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>【活動期間】7/1–7/25
+【主打商品】即飲果醋 + 蒟蒻飲組合
+【優惠】任選 2 件 9 折 + 蝦幣回饋
+【配合動作】訂單包裝內夾官網入會 QR Code 卡</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>上架前確認商品頁圖片與活動標籤設定</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>訂單數、新客比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2025/7/25</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>活動收尾</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>好食節收尾倒數｜8 月中元預告</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>【動作】更新商品頁 Banner 預告 8 月中元活動
+【文案方向】「好食節感謝，中元好料即將登場」
+【注意】確保庫存備貨到位</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>更新蝦皮店頭 Banner</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>下午 2:00</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>頁面瀏覽數</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/10</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>活動預告</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購倒數預告｜8/12–8/14 每天 2 小時限時</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>【預告內容】8/12、8/13、8/14 每天 14:00–16:00 閃購
+【主打商品】味噌 + 烏醋 + 辣椒醬三件組
+【預告動作】限時動態 + 商品頁倒數標籤</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>設定蝦皮閃購時段，確認庫存</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>加購清單數</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>2025/8/10</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>商品上架</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>中元禮盒上架｜滿 1,200 免運 + 贈品</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>【商品】中元天然調味禮盒（味噌 + 烏醋 + 辣椒醬）
+【定價】與官網同步
+【優惠】滿 1,200 免運 + 贈品（小包裝試用品）
+【圖片】使用官網禮盒實物圖</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>確認 MOMO 商品頁審核通過，圖片規格符合平台要求</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>商品頁瀏覽數、加購數</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/12</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 1｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【商品】味噌 + 烏醋 + 辣椒醬三件組
+【配合】同步在 LINE OA 提醒好友</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>閃購期間監控庫存與訂單狀況</t>
+        </is>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/13</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 2｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【商品】同 Day 1
+【加碼】留評價送小禮（若庫存允許）</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>確認 Day 1 庫存餘量，調整 Day 2 數量</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、評價數</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>2025/8/14</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>限時閃購</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>中元閃購 Day 3（最終場）｜14:00–16:00</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>【時段】14:00–16:00
+【折扣】限時 85 折
+【文案】「今天最後一場，明天恢復原價」
+【配合】FB + LINE OA 最後提醒</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>最後一天加強社群提醒力道</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>閃購訂單數、三天累計 GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>2025/8/15</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>節慶衝單</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>中元禮盒主力日｜配合抽獎公告衝單</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>【動作】配合 FB + LINE 抽獎公告，在 MOMO 同步推廣
+【文案方向】「送禮送健康，天然調味全家用」
+【可申請】MOMO 節慶聯合檔期（若有補貼）</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>查詢 MOMO 8 月是否有聯合檔期補貼可申請</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>當日訂單數、禮盒銷售佔比</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>2025/9/12</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>正式開賣</t>
+        </is>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>中秋禮盒正式開賣（與官網同步）</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>【動作】早鳥結束，恢復原價開賣
+【配合】FB + LINE OA 同步公告
+【文案】「中秋送禮，天然調味料用一整年」
+【注意】確保物流在中秋前 3 天可到貨</t>
+        </is>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>確認物流時效，中秋前 3 天截單</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J10" s="34" t="inlineStr">
+        <is>
+          <t>中秋期間總訂單數、GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/12</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>節慶衝單</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>中秋正式開賣｜主力推廣日</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>【動作】與蝦皮、官網同步開賣
+【MOMO 特色】主打禮盒送禮情境，文案偏「送給爸媽」
+【可申請】MOMO 中秋聯合檔期（若有補貼）</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>查詢 MOMO 9 月中秋聯合檔期補貼，截止申請日期</t>
+        </is>
+      </c>
+      <c r="I11" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J11" s="36" t="inlineStr">
+        <is>
+          <t>當日訂單數、GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/17</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>活動收尾</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>中秋禮盒最後衝刺｜中秋前 2 天截單</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>【動作】更新商品頁「中秋前 2 天下單才來得及」緊迫文案
+【配合】FB + LINE 同步提醒
+【截單時間】9/17 23:59</t>
+        </is>
+      </c>
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>確認物流可在 9/19 前到貨，超過截止下架禮盒</t>
+        </is>
+      </c>
+      <c r="I12" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J12" s="36" t="inlineStr">
+        <is>
+          <t>最終累計訂單數、中秋期間總 GMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>2025/9/8</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>蝦皮</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>早鳥預購</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>中秋早鳥預購開始｜9/8–9/10 限定 9 折</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>【活動期間】9/8–9/10
+【折扣】早鳥 9 折
+【主打商品】味噌 + 味醂 + 烏醋 + 米醋四件組
+【加碼】前 100 組附「烤肉醬食譜卡」
+【定價原則】不低於官網會員價</t>
+        </is>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>設定早鳥折扣碼，確認食譜卡印製數量</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J13" s="34" t="inlineStr">
+        <is>
+          <t>預購訂單數</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>2025/9/8</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>MOMO</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>商品上架</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>中秋禮盒上架｜滿 2,000 加購優惠</t>
+        </is>
+      </c>
+      <c r="G14" s="36" t="inlineStr">
+        <is>
+          <t>【商品】中秋天然調味禮盒（味噌 + 味醂 + 烏醋 + 米醋四件組）
+【優惠】滿 2,000 加購第二件 75 折
+【目標客群】30–55 歲，送禮給長輩或朋友</t>
+        </is>
+      </c>
+      <c r="H14" s="36" t="inlineStr">
+        <is>
+          <t>確認 MOMO 商品頁上架，主圖需有中秋氛圍</t>
+        </is>
+      </c>
+      <c r="I14" s="35" t="inlineStr">
+        <is>
+          <t>上午 10:00</t>
+        </is>
+      </c>
+      <c r="J14" s="36" t="inlineStr">
+        <is>
+          <t>商品頁瀏覽數、加購數</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>顏色</t>
         </is>
@@ -5286,7 +6826,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="50" t="inlineStr">
         <is>
           <t>淺藍</t>
         </is>
@@ -5298,7 +6838,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>淺綠</t>
         </is>
@@ -5310,7 +6850,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>淺黃</t>
         </is>
@@ -5322,9 +6862,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
-        <is>
-          <t>淺橘 1</t>
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>淺橘</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5334,9 +6874,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>淺橘 2</t>
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>中橘</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5346,7 +6886,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>深橘</t>
         </is>
@@ -5358,110 +6898,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>紅色類型</t>
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>淺珊瑚</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>活動類</t>
+          <t>蝦皮 7 月</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>橘色類型</t>
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>中珊瑚</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>食譜類</t>
+          <t>蝦皮 8 月</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>粉紫類型</t>
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>深珊瑚</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>知識類</t>
+          <t>蝦皮 9 月</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>淺紫欄</t>
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>淺紫</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Olivia 配圖方向（FB Sheet 第 10-11 欄）</t>
+          <t>MOMO 7 月</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>中紫</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MOMO 8 月</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>深紫</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MOMO 9 月</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Sheet 說明</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>📅 綜合排程月曆</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FB + LINE OA 所有內容按日期合併，直接用於排程</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FB + LINE OA + 蝦皮 + MOMO 全通路按日期合併</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>📘 FB 貼文完整稿</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>FB 24 篇含 Olivia 配圖方向</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>💬 LINE OA 推播完整稿</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>13 則定期推播訊息</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="50" t="inlineStr">
         <is>
           <t>🤖 LINE 自動序列</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>新好友加入後的 3 則自動回覆（需在 LINE OA 後台設定）</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>新好友加入後的 3 則自動回覆</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="inlineStr">
+        <is>
+          <t>🛒 蝦皮MOMO活動完整稿</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>蝦皮 8 則 + MOMO 5 則，共 13 筆活動</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>重要原則</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr">
+        <is>
+          <t>定價</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>蝦皮 / MOMO 售價 ≥ 官網原價，保護會員制稀缺性</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
+        <is>
+          <t>時序</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>官網會員 → LINE OA → 蝦皮 = MOMO → FB，會員永遠最早</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="inlineStr">
+        <is>
+          <t>導流</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>每筆蝦皮 / MOMO 訂單包裝夾「官網入會 QR Code 卡」</t>
         </is>
       </c>
     </row>

--- a/十全特好_7-9月完整排程月曆.xlsx
+++ b/十全特好_7-9月完整排程月曆.xlsx
@@ -912,17 +912,18 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>舊好友喚醒：一鍵加入官網會員</t>
+          <t>買了 5 入味噌的你，抽獎資格還沒領</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>你加入我們 LINE 已經一段時間了。
-但 88 元折扣券你拿到了嗎？
-用 LINE 帳號一鍵加入官網會員，
-券馬上匯入，7/15 抽獎資格也一起有。
-這次沒加入，就真的沒了。
-👇 點這裡，10 秒完成</t>
+          <t>七月有個抽獎活動，你可能有資格。
+參加方式：
+購買 5 入味噌 → 包裝內取得抽獎卡 → 進活動頁完成官網會員 → 抽獎資格到手。
+已經買了 5 入味噌的，現在完成官網會員就好，10 秒搞定。
+還沒買的，全聯、官網都有，7/15 開抽前都來得及。
+加入會員同時送 88 元折扣券，立刻入帳。
+👇 點這裡完成會員資格</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr"/>
@@ -5372,17 +5373,18 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>舊好友喚醒：一鍵加入官網會員</t>
+          <t>買了 5 入味噌的你，抽獎資格還沒領</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>你加入我們 LINE 已經一段時間了。
-但 88 元折扣券你拿到了嗎？
-用 LINE 帳號一鍵加入官網會員，
-券馬上匯入，7/15 抽獎資格也一起有。
-這次沒加入，就真的沒了。
-👇 點這裡，10 秒完成</t>
+          <t>七月有個抽獎活動，你可能有資格。
+參加方式：
+購買 5 入味噌 → 包裝內取得抽獎卡 → 進活動頁完成官網會員 → 抽獎資格到手。
+已經買了 5 入味噌的，現在完成官網會員就好，10 秒搞定。
+還沒買的，全聯、官網都有，7/15 開抽前都來得及。
+加入會員同時送 88 元折扣券，立刻入帳。
+👇 點這裡完成會員資格</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
